--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
